--- a/data/trans_orig/Q25B01-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/Q25B01-Estudios-trans_orig.xlsx
@@ -526,7 +526,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Número medio de cigarrillos que fumaban antes de haber dejado de fumar</t>
+          <t>Número medio de cigarrillos que fumaban antes de haber dejado de fumar (tasa de respuesta: 96,93%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>23,34; 26,46</t>
+          <t>23,43; 26,48</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>24,43; 28,06</t>
+          <t>24,45; 27,98</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>21,17; 25,23</t>
+          <t>21,22; 25,62</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>20,78; 24,48</t>
+          <t>20,98; 24,53</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>11,64; 17,61</t>
+          <t>11,99; 17,88</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>9,96; 14,79</t>
+          <t>9,65; 14,39</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>10,22; 15,55</t>
+          <t>10,24; 15,62</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>12,32; 16,86</t>
+          <t>12,28; 16,91</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>22,04; 24,72</t>
+          <t>22,0; 24,84</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>22,31; 25,75</t>
+          <t>22,46; 25,78</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>19,7; 23,47</t>
+          <t>19,77; 23,37</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>19,45; 22,61</t>
+          <t>19,48; 22,51</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>18,33; 21,26</t>
+          <t>18,48; 21,27</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>19,59; 22,64</t>
+          <t>19,79; 22,66</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>20,23; 23,29</t>
+          <t>20,16; 23,3</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>19,23; 21,91</t>
+          <t>19,29; 21,79</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>10,9; 13,83</t>
+          <t>10,95; 13,74</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>12,92; 16,02</t>
+          <t>12,95; 15,81</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>12,8; 15,39</t>
+          <t>12,76; 15,4</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>11,04; 13,1</t>
+          <t>10,98; 13,02</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>15,85; 17,98</t>
+          <t>15,74; 18,05</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>17,22; 19,43</t>
+          <t>17,23; 19,45</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>17,47; 19,87</t>
+          <t>17,39; 19,74</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>16,61; 19,32</t>
+          <t>16,74; 19,39</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>18,2; 24,22</t>
+          <t>18,04; 24,15</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>16,49; 22,61</t>
+          <t>16,38; 22,84</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>15,71; 21,38</t>
+          <t>15,73; 21,38</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>16,71; 20,85</t>
+          <t>16,64; 20,8</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>10,21; 14,03</t>
+          <t>10,19; 13,75</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>10,28; 14,13</t>
+          <t>10,39; 14,18</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>10,27; 14,63</t>
+          <t>10,52; 14,75</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>10,52; 14,16</t>
+          <t>10,52; 14,07</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>15,65; 20,01</t>
+          <t>15,79; 20,25</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>14,34; 18,46</t>
+          <t>14,21; 18,17</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>13,39; 17,13</t>
+          <t>13,52; 17,37</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>14,79; 17,77</t>
+          <t>14,66; 17,64</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>21,4; 23,44</t>
+          <t>21,36; 23,45</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>22,11; 24,47</t>
+          <t>22,08; 24,29</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>20,45; 22,79</t>
+          <t>20,53; 22,86</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>19,77; 21,53</t>
+          <t>19,67; 21,45</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>11,56; 13,83</t>
+          <t>11,64; 13,87</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>12,41; 14,62</t>
+          <t>12,44; 14,52</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>12,38; 14,36</t>
+          <t>12,37; 14,45</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>11,47; 13,2</t>
+          <t>11,52; 13,16</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>18,72; 20,4</t>
+          <t>18,81; 20,59</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>19,22; 21,0</t>
+          <t>19,14; 20,9</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>17,82; 19,51</t>
+          <t>17,81; 19,65</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>17,39; 19,18</t>
+          <t>17,34; 19,12</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/Q25B01-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/Q25B01-Estudios-trans_orig.xlsx
@@ -663,7 +663,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>22,69</t>
+          <t>22,7</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -683,7 +683,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>14,41</t>
+          <t>14,31</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>23,43; 26,48</t>
+          <t>23,43; 26,33</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>24,45; 27,98</t>
+          <t>24,23; 27,9</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>21,22; 25,62</t>
+          <t>21,31; 25,61</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>20,98; 24,53</t>
+          <t>20,85; 24,39</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>11,99; 17,88</t>
+          <t>11,91; 17,39</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>9,65; 14,39</t>
+          <t>9,86; 14,58</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>10,24; 15,62</t>
+          <t>10,21; 15,59</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>12,28; 16,91</t>
+          <t>12,28; 16,86</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>22,0; 24,84</t>
+          <t>21,86; 24,6</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>22,46; 25,78</t>
+          <t>22,4; 25,7</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>19,77; 23,37</t>
+          <t>19,73; 23,36</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>19,48; 22,51</t>
+          <t>19,55; 22,54</t>
         </is>
       </c>
     </row>
@@ -803,7 +803,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>20,33</t>
+          <t>20,24</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -843,7 +843,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>18,05</t>
+          <t>16,92</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>18,48; 21,27</t>
+          <t>18,35; 21,18</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>19,79; 22,66</t>
+          <t>19,71; 22,75</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>20,16; 23,3</t>
+          <t>20,13; 23,51</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>19,29; 21,79</t>
+          <t>18,78; 21,83</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>10,95; 13,74</t>
+          <t>10,9; 13,9</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>12,95; 15,81</t>
+          <t>12,97; 16,02</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>12,76; 15,4</t>
+          <t>12,73; 15,35</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>10,98; 13,02</t>
+          <t>10,97; 13,02</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>15,74; 18,05</t>
+          <t>15,74; 17,94</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>17,23; 19,45</t>
+          <t>17,15; 19,38</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>17,39; 19,74</t>
+          <t>17,57; 19,87</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>16,74; 19,39</t>
+          <t>15,92; 18,1</t>
         </is>
       </c>
     </row>
@@ -943,7 +943,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>18,7</t>
+          <t>18,91</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>12,14</t>
+          <t>12,08</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>16,15</t>
+          <t>16,24</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>18,04; 24,15</t>
+          <t>18,38; 24,21</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>16,38; 22,84</t>
+          <t>16,51; 22,62</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>15,73; 21,38</t>
+          <t>15,62; 21,28</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>16,64; 20,8</t>
+          <t>17,0; 21,03</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>10,19; 13,75</t>
+          <t>10,19; 13,92</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>10,39; 14,18</t>
+          <t>10,53; 14,3</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>10,52; 14,75</t>
+          <t>10,46; 15,09</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>10,52; 14,07</t>
+          <t>10,53; 13,98</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>15,79; 20,25</t>
+          <t>15,71; 19,75</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>14,21; 18,17</t>
+          <t>14,24; 18,09</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>13,52; 17,37</t>
+          <t>13,67; 17,39</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>14,66; 17,64</t>
+          <t>14,85; 17,86</t>
         </is>
       </c>
     </row>
@@ -1083,7 +1083,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>20,53</t>
+          <t>20,6</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1103,7 +1103,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>12,33</t>
+          <t>12,3</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>18,21</t>
+          <t>17,64</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>21,36; 23,45</t>
+          <t>21,37; 23,38</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>22,08; 24,29</t>
+          <t>22,06; 24,33</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>20,53; 22,86</t>
+          <t>20,47; 22,84</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>19,67; 21,45</t>
+          <t>19,74; 21,78</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>11,64; 13,87</t>
+          <t>11,5; 13,83</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>12,44; 14,52</t>
+          <t>12,42; 14,58</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>12,37; 14,45</t>
+          <t>12,37; 14,41</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>11,52; 13,16</t>
+          <t>11,44; 13,12</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>18,81; 20,59</t>
+          <t>18,73; 20,44</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>19,14; 20,9</t>
+          <t>19,21; 21,02</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>17,81; 19,65</t>
+          <t>17,8; 19,64</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>17,34; 19,12</t>
+          <t>16,91; 18,41</t>
         </is>
       </c>
     </row>
